--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132692254</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,6 +771,131 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123324305</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grossjömyren, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>608307</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6988780</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2024_1314</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132692254</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,8 +908,17 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123324305</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132692254</v>
+        <v>135427244</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grössjöberget, Ång</t>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608355</v>
+        <v>608286</v>
       </c>
       <c r="R2" t="n">
-        <v>6988727</v>
+        <v>6988804</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,78 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132692254</t>
+          <t>https://artportalen.se/Sighting/135427244</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324305</v>
+        <v>135427838</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grossjömyren, Ång</t>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608307</v>
+        <v>608356</v>
       </c>
       <c r="R3" t="n">
-        <v>6988780</v>
+        <v>6988724</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,29 +845,14 @@
           <t>Graninge</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2024_1314</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,22 +867,3800 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427838</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132692254</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>608355</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6988727</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristin Lindström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristin Lindström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132692254</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135427304</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608279</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6988797</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427304</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135427626</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608315</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6988755</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427626</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135427660</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>608317</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6988732</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427660</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135427716</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608344</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6988703</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427716</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135427832</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608350</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6988730</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427832</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135428289</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>608345</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6988598</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428289</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135428921</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>608297</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6988502</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428921</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135428954</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92016</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>608291</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6988501</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428954</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135427239</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92448</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>608286</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6988804</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427239</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135427351</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92360</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>608285</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6988794</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427351</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135427640</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>608319</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6988754</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427640</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135427668</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>608317</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6988731</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427668</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135427721</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>608332</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6988722</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427721</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135427800</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>608347</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6988737</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427800</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135427982</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>608290</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6988733</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427982</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135428054</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>608296</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6988749</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428054</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135428336</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>608355</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6988585</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428336</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135428626</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91979</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>608316</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6988600</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428626</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123324305</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Grossjömyren, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>608307</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6988780</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2024_1314</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123324305</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135427273</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>608282</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6988798</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427273</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135427406</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>608305</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6988782</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427406</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135427422</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>608306</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6988753</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427422</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135427918</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>608314</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6988709</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427918</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135428378</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>608310</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6988606</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428378</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135429124</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79411</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>608259</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6988539</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429124</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135427934</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80526</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>608314</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6988710</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427934</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135427938</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80531</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>608316</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6988712</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427938</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135428156</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>608289</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6988697</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428156</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135428168</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>608289</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6988698</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428168</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135428184</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>608292</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6988699</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428184</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135428213</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>608315</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6988657</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428213</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135428801</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>608346</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6988570</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428801</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135429081</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>608279</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6988519</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429081</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135429266</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>608171</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6988579</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429266</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135428037</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>608293</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6988743</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428037</t>
         </is>
       </c>
     </row>
@@ -918,6 +4668,42 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135427244</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135427838</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>135427304</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>135427626</v>
       </c>
       <c r="B6" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>135427660</v>
       </c>
       <c r="B7" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>135427716</v>
       </c>
       <c r="B8" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>135427832</v>
       </c>
       <c r="B9" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135428289</v>
       </c>
       <c r="B10" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>135428921</v>
       </c>
       <c r="B11" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>135428954</v>
       </c>
       <c r="B12" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>135427239</v>
       </c>
       <c r="B13" t="n">
-        <v>92448</v>
+        <v>92475</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>135427351</v>
       </c>
       <c r="B14" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>135427640</v>
       </c>
       <c r="B15" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>135427668</v>
       </c>
       <c r="B16" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>135427721</v>
       </c>
       <c r="B17" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>135427800</v>
       </c>
       <c r="B18" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>135427982</v>
       </c>
       <c r="B19" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>135428054</v>
       </c>
       <c r="B20" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>135428336</v>
       </c>
       <c r="B21" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>135428626</v>
       </c>
       <c r="B22" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>135427273</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135427406</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>135427422</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>135427918</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>135428378</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>135429124</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>135427934</v>
       </c>
       <c r="B30" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>135427938</v>
       </c>
       <c r="B31" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>135428037</v>
       </c>
       <c r="B39" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132692254</v>
+        <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grössjöberget, Ång</t>
+          <t>Nyslåtten, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608355</v>
+        <v>608338</v>
       </c>
       <c r="R2" t="n">
-        <v>6988727</v>
+        <v>6988735</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,78 +775,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristin Lindström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132692254</t>
+          <t>https://artportalen.se/Sighting/135742971</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123324305</v>
+        <v>135427244</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grossjömyren, Ång</t>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608307</v>
+        <v>608286</v>
       </c>
       <c r="R3" t="n">
-        <v>6988780</v>
+        <v>6988804</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,29 +855,14 @@
           <t>Graninge</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2024_1314</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,22 +877,5027 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427244</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135427838</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92319</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>658</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>608356</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6988724</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427838</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135742972</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92319</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608338</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6988735</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742972</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132692254</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91974</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608355</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6988727</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristin Lindström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristin Lindström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132692254</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135427304</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>608279</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6988797</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427304</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135427626</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608315</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6988755</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427626</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135427660</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608317</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6988732</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427660</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135427716</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>608344</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6988703</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427716</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135427832</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>608350</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6988730</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427832</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135428289</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>608345</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6988598</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428289</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135428921</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>608297</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6988502</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428921</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135428954</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>608291</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6988501</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428954</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135742973</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>608337</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6988735</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742973</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135427239</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92480</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>608286</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6988804</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427239</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135742974</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>608315</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6988755</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742974</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135742991</v>
+      </c>
+      <c r="B18" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>608281</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6988809</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742991</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135427351</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92392</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>608285</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6988794</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427351</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135427640</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>608319</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6988754</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427640</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135427668</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>608317</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6988731</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427668</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135427721</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>608332</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6988722</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427721</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135427800</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>608347</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6988737</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427800</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135427982</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>608290</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6988733</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427982</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135428054</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>608296</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6988749</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428054</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135428336</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>608355</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6988585</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428336</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135428626</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>608316</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6988600</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428626</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123324305</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Grossjömyren, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>608307</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6988780</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2024_1314</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>David Isaksson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY28" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123324305</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135427273</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>608282</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6988798</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427273</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135427406</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>608305</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6988782</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427406</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135427422</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>608306</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6988753</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427422</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135427918</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>608314</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6988709</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427918</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135428378</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>608310</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6988606</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428378</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135429124</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>608259</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6988539</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429124</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135742992</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>608281</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6988809</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742992</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135742994</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>608388</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6988689</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742994</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135742975</v>
+      </c>
+      <c r="B37" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>608313</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6988758</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742975</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135742995</v>
+      </c>
+      <c r="B38" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>608381</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6988641</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742995</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135427934</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>608314</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6988710</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427934</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135427938</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>608316</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6988712</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135427938</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135742970</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80567</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>608311</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6988718</v>
+      </c>
+      <c r="S41" t="n">
+        <v>7</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742970</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135428156</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>608289</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6988697</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428156</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135428168</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>608289</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6988698</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428168</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135428184</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>608292</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6988699</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428184</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135428213</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>608315</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6988657</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428213</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135428801</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>608346</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6988570</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428801</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135429081</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>608279</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6988519</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429081</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135429266</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>608171</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6988579</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135429266</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135742993</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>608321</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6988717</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1 ex läte</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135742993</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135428037</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Nyslåtten, Nyslåtten, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>608293</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6988743</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135428037</t>
         </is>
       </c>
     </row>
@@ -918,6 +5905,53 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135427244</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135427838</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135742972</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>135427304</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>135427626</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>135427660</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>135427716</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135427832</v>
       </c>
       <c r="B11" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135428289</v>
       </c>
       <c r="B12" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135428921</v>
       </c>
       <c r="B13" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135428954</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135742973</v>
       </c>
       <c r="B15" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135427239</v>
       </c>
       <c r="B16" t="n">
-        <v>92480</v>
+        <v>92482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135427351</v>
       </c>
       <c r="B19" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135427640</v>
       </c>
       <c r="B20" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135427668</v>
       </c>
       <c r="B21" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135427721</v>
       </c>
       <c r="B22" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>135427800</v>
       </c>
       <c r="B23" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135427982</v>
       </c>
       <c r="B24" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>135428054</v>
       </c>
       <c r="B25" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>135428336</v>
       </c>
       <c r="B26" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>135428626</v>
       </c>
       <c r="B27" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>135428037</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135427244</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135427838</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135742972</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>135427304</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>135427626</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>135427660</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>135427716</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135427832</v>
       </c>
       <c r="B11" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135428289</v>
       </c>
       <c r="B12" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135428921</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135428954</v>
       </c>
       <c r="B14" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135742973</v>
       </c>
       <c r="B15" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135427239</v>
       </c>
       <c r="B16" t="n">
-        <v>92482</v>
+        <v>92496</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135742974</v>
       </c>
       <c r="B17" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135742991</v>
       </c>
       <c r="B18" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135427351</v>
       </c>
       <c r="B19" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135427640</v>
       </c>
       <c r="B20" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135427668</v>
       </c>
       <c r="B21" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135427721</v>
       </c>
       <c r="B22" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>135427800</v>
       </c>
       <c r="B23" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135427982</v>
       </c>
       <c r="B24" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>135428054</v>
       </c>
       <c r="B25" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>135428336</v>
       </c>
       <c r="B26" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>135428626</v>
       </c>
       <c r="B27" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>135427273</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135427406</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>135427422</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>135427918</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135428378</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135429124</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>135742992</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135742994</v>
       </c>
       <c r="B36" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>135742975</v>
       </c>
       <c r="B37" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135742995</v>
       </c>
       <c r="B38" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>135427934</v>
       </c>
       <c r="B39" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>135427938</v>
       </c>
       <c r="B40" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>135742970</v>
       </c>
       <c r="B41" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>135428156</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>135428168</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>135428184</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>135428213</v>
       </c>
       <c r="B45" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>135428801</v>
       </c>
       <c r="B46" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>135429081</v>
       </c>
       <c r="B47" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>135429266</v>
       </c>
       <c r="B48" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135742993</v>
       </c>
       <c r="B49" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>135428037</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>92684</v>
+        <v>92685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135427244</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135427838</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135742972</v>
       </c>
       <c r="B5" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>135427304</v>
       </c>
       <c r="B7" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>135427626</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>135427660</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>135427716</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135427832</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135428289</v>
       </c>
       <c r="B12" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135428921</v>
       </c>
       <c r="B13" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135428954</v>
       </c>
       <c r="B14" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135742973</v>
       </c>
       <c r="B15" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135427239</v>
       </c>
       <c r="B16" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135742974</v>
       </c>
       <c r="B17" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135742991</v>
       </c>
       <c r="B18" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135427351</v>
       </c>
       <c r="B19" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135427640</v>
       </c>
       <c r="B20" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135427668</v>
       </c>
       <c r="B21" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135427721</v>
       </c>
       <c r="B22" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>135427800</v>
       </c>
       <c r="B23" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135427982</v>
       </c>
       <c r="B24" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>135428054</v>
       </c>
       <c r="B25" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>135428336</v>
       </c>
       <c r="B26" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>135428626</v>
       </c>
       <c r="B27" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>135427273</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135427406</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>135427422</v>
       </c>
       <c r="B31" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>135427918</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135428378</v>
       </c>
       <c r="B33" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135429124</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>135742992</v>
       </c>
       <c r="B35" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135742994</v>
       </c>
       <c r="B36" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>135742975</v>
       </c>
       <c r="B37" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135742995</v>
       </c>
       <c r="B38" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>135427934</v>
       </c>
       <c r="B39" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>135427938</v>
       </c>
       <c r="B40" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>135742970</v>
       </c>
       <c r="B41" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>135428037</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>92685</v>
+        <v>92686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135427244</v>
       </c>
       <c r="B3" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135427838</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135742972</v>
       </c>
       <c r="B5" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>135427304</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>135427626</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>135427660</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>135427716</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135427832</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135428289</v>
       </c>
       <c r="B12" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135428921</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135428954</v>
       </c>
       <c r="B14" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135742973</v>
       </c>
       <c r="B15" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135427239</v>
       </c>
       <c r="B16" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135427351</v>
       </c>
       <c r="B19" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135427640</v>
       </c>
       <c r="B20" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135427668</v>
       </c>
       <c r="B21" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135427721</v>
       </c>
       <c r="B22" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>135427800</v>
       </c>
       <c r="B23" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135427982</v>
       </c>
       <c r="B24" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>135428054</v>
       </c>
       <c r="B25" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>135428336</v>
       </c>
       <c r="B26" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>135428626</v>
       </c>
       <c r="B27" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>135428037</v>
       </c>
       <c r="B50" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>92686</v>
+        <v>92687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135427244</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135427838</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135742972</v>
       </c>
       <c r="B5" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>135427304</v>
       </c>
       <c r="B7" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>135427626</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>135427660</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>135427716</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135427832</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135428289</v>
       </c>
       <c r="B12" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135428921</v>
       </c>
       <c r="B13" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135428954</v>
       </c>
       <c r="B14" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135742973</v>
       </c>
       <c r="B15" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135427239</v>
       </c>
       <c r="B16" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135742974</v>
       </c>
       <c r="B17" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135742991</v>
       </c>
       <c r="B18" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135427351</v>
       </c>
       <c r="B19" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135427640</v>
       </c>
       <c r="B20" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135427668</v>
       </c>
       <c r="B21" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135427721</v>
       </c>
       <c r="B22" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>135427800</v>
       </c>
       <c r="B23" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135427982</v>
       </c>
       <c r="B24" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>135428054</v>
       </c>
       <c r="B25" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>135428336</v>
       </c>
       <c r="B26" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>135428626</v>
       </c>
       <c r="B27" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>135427273</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135427406</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>135427422</v>
       </c>
       <c r="B31" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>135427918</v>
       </c>
       <c r="B32" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135428378</v>
       </c>
       <c r="B33" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135429124</v>
       </c>
       <c r="B34" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>135742992</v>
       </c>
       <c r="B35" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135742994</v>
       </c>
       <c r="B36" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>135742975</v>
       </c>
       <c r="B37" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135742995</v>
       </c>
       <c r="B38" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>135427934</v>
       </c>
       <c r="B39" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>135427938</v>
       </c>
       <c r="B40" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>135742970</v>
       </c>
       <c r="B41" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>135428156</v>
       </c>
       <c r="B42" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>135428168</v>
       </c>
       <c r="B43" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>135428184</v>
       </c>
       <c r="B44" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>135428213</v>
       </c>
       <c r="B45" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>135428801</v>
       </c>
       <c r="B46" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>135429081</v>
       </c>
       <c r="B47" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>135429266</v>
       </c>
       <c r="B48" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135742993</v>
       </c>
       <c r="B49" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>135428037</v>
       </c>
       <c r="B50" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>92687</v>
+        <v>92693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135427244</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135427838</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135742972</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>135427304</v>
       </c>
       <c r="B7" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>135427626</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>135427660</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>135427716</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>135427832</v>
       </c>
       <c r="B11" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135428289</v>
       </c>
       <c r="B12" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>135428921</v>
       </c>
       <c r="B13" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>135428954</v>
       </c>
       <c r="B14" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135742973</v>
       </c>
       <c r="B15" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135427239</v>
       </c>
       <c r="B16" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135742974</v>
       </c>
       <c r="B17" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135742991</v>
       </c>
       <c r="B18" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>135427351</v>
       </c>
       <c r="B19" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>135427640</v>
       </c>
       <c r="B20" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>135427668</v>
       </c>
       <c r="B21" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         <v>135427721</v>
       </c>
       <c r="B22" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
         <v>135427800</v>
       </c>
       <c r="B23" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135427982</v>
       </c>
       <c r="B24" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>135428054</v>
       </c>
       <c r="B25" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>135428336</v>
       </c>
       <c r="B26" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>135428626</v>
       </c>
       <c r="B27" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>135427273</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135427406</v>
       </c>
       <c r="B30" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>135427422</v>
       </c>
       <c r="B31" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>135427918</v>
       </c>
       <c r="B32" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>135428378</v>
       </c>
       <c r="B33" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135429124</v>
       </c>
       <c r="B34" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>135742992</v>
       </c>
       <c r="B35" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135742994</v>
       </c>
       <c r="B36" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>135742975</v>
       </c>
       <c r="B37" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135742995</v>
       </c>
       <c r="B38" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>135427934</v>
       </c>
       <c r="B39" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>135427938</v>
       </c>
       <c r="B40" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>135742970</v>
       </c>
       <c r="B41" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4899,7 +4899,7 @@
         <v>135428156</v>
       </c>
       <c r="B42" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>135428168</v>
       </c>
       <c r="B43" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>135428184</v>
       </c>
       <c r="B44" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>135428213</v>
       </c>
       <c r="B45" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>135428801</v>
       </c>
       <c r="B46" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>135429081</v>
       </c>
       <c r="B47" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>135429266</v>
       </c>
       <c r="B48" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135742993</v>
       </c>
       <c r="B49" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5795,7 +5795,7 @@
         <v>135428037</v>
       </c>
       <c r="B50" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>92693</v>
+        <v>92694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135742972</v>
       </c>
       <c r="B5" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135742973</v>
       </c>
       <c r="B15" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135742974</v>
       </c>
       <c r="B17" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135742991</v>
       </c>
       <c r="B18" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>135742992</v>
       </c>
       <c r="B35" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135742994</v>
       </c>
       <c r="B36" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>135742975</v>
       </c>
       <c r="B37" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135742995</v>
       </c>
       <c r="B38" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>135742970</v>
       </c>
       <c r="B41" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135742993</v>
       </c>
       <c r="B49" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>92694</v>
+        <v>92700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135742972</v>
       </c>
       <c r="B5" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135742973</v>
       </c>
       <c r="B15" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135742974</v>
       </c>
       <c r="B17" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135742991</v>
       </c>
       <c r="B18" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>135742992</v>
       </c>
       <c r="B35" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135742994</v>
       </c>
       <c r="B36" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>135742975</v>
       </c>
       <c r="B37" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135742995</v>
       </c>
       <c r="B38" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>135742970</v>
       </c>
       <c r="B41" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 37018-2025 artfynd.xlsx
+++ b/artfynd/A 37018-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135742971</v>
       </c>
       <c r="B2" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135742972</v>
       </c>
       <c r="B5" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135742973</v>
       </c>
       <c r="B15" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>135742974</v>
       </c>
       <c r="B17" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>135742991</v>
       </c>
       <c r="B18" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>135742992</v>
       </c>
       <c r="B35" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>135742994</v>
       </c>
       <c r="B36" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>135742975</v>
       </c>
       <c r="B37" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>135742995</v>
       </c>
       <c r="B38" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>135742970</v>
       </c>
       <c r="B41" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         <v>135742993</v>
       </c>
       <c r="B49" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
